--- a/calculation_forms/022_retirement_savings_calculator--calculation_forms.xlsx
+++ b/calculation_forms/022_retirement_savings_calculator--calculation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Retirement Age</t>
+          <t>Retirement Age (2)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>retirement_goal_age</t>
+          <t>retirement_goal_age_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Retirement Goal Age</t>
+          <t>Retirement Goal Age 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>monthly_savings_rate</t>
+          <t>monthly_savings_rate_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>years_retirement_age</t>
+          <t>years_retirement_age_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Years in Retirement</t>
+          <t>Years Retirement Age 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>monthly_inflation_rate</t>
+          <t>monthly_inflation_rate_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monthly Inflation Rate</t>
+          <t>Monthly Inflation Rate 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>retirement_income_source</t>
+          <t>retirement_income_source_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Income Source</t>
+          <t>Retirement Income Source 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>inflation_rate</t>
+          <t>inflation_rate_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Inflation Rate</t>
+          <t>Inflation Rate 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>years_in_retirement</t>
+          <t>years_in_retirement_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Years in Retirement</t>
+          <t>Years In Retirement 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1194,7 +1194,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>retirement_income_source_choices</t>
+          <t>retirement_income_source_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>retirement_income_source_choices</t>
+          <t>retirement_income_source_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1228,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>retirement_income_source_choices</t>
+          <t>retirement_income_source_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>retirement_income_source_choices</t>
+          <t>retirement_income_source_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
